--- a/data/trans_camb/P38C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Provincia-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,2; 32,8</t>
+          <t>20,21; 32,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,51; 27,84</t>
+          <t>17,59; 27,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 28,53</t>
+          <t>20,5; 28,44</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,57; 50,54</t>
+          <t>26,75; 50,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 39,11</t>
+          <t>21,88; 39,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 41,08</t>
+          <t>26,88; 40,88</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -7,06</t>
+          <t>-20,96; -7,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,29; -6,55</t>
+          <t>-14,02; -5,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,13; -7,92</t>
+          <t>-15,49; -8,1</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -8,18</t>
+          <t>-23,33; -8,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -7,03</t>
+          <t>-14,69; -6,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,51; -8,8</t>
+          <t>-17,03; -8,97</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 8,7</t>
+          <t>-0,42; 8,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,78</t>
+          <t>1,65; 8,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,75</t>
+          <t>1,96; 7,7</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 10,05</t>
+          <t>-0,49; 10,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,8</t>
+          <t>1,71; 9,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,68</t>
+          <t>2,18; 8,62</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -0,67</t>
+          <t>-15,6; -0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 2,06</t>
+          <t>-46,34; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -1,27</t>
+          <t>-32,22; -1,1</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -0,78</t>
+          <t>-16,87; -1,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 2,28</t>
+          <t>-49,69; 1,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,15; -1,39</t>
+          <t>-34,92; -1,19</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 12,85</t>
+          <t>-4,11; 11,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 5,2</t>
+          <t>-5,59; 5,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,98</t>
+          <t>-2,62; 7,18</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 17,86</t>
+          <t>-5,12; 16,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 6,16</t>
+          <t>-6,16; 6,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,7</t>
+          <t>-3,01; 9,06</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,71</t>
+          <t>8,81; 20,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,9; 14,48</t>
+          <t>5,32; 14,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,01</t>
+          <t>8,88; 15,76</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11,41; 27,55</t>
+          <t>10,88; 26,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6,53; 17,42</t>
+          <t>5,88; 16,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10,45; 19,52</t>
+          <t>10,25; 19,38</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,75; 22,97</t>
+          <t>10,93; 23,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15,66; 26,33</t>
+          <t>14,9; 25,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,25; 24,75</t>
+          <t>15,25; 24,35</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,26; 37,09</t>
+          <t>16,41; 37,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20,67; 37,51</t>
+          <t>19,56; 35,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,52; 36,57</t>
+          <t>21,45; 36,24</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-69,86; -25,85</t>
+          <t>-69,04; -25,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-28,32; -21,26</t>
+          <t>-28,34; -21,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-56,92; -25,32</t>
+          <t>-56,99; -25,28</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-77,52; -29,2</t>
+          <t>-76,86; -29,23</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -22,68</t>
+          <t>-29,93; -22,53</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -27,61</t>
+          <t>-62,12; -27,55</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -0,38</t>
+          <t>-22,03; -0,25</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 1,64</t>
+          <t>-6,64; 1,35</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 0,07</t>
+          <t>-11,95; 0,01</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -0,46</t>
+          <t>-27,36; -0,3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,88</t>
+          <t>-7,62; 1,54</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 0,09</t>
+          <t>-14,14; -0,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38C-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P38C-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>26,42</t>
+          <t>26,9</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22,35</t>
+          <t>22,59</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,37</t>
+          <t>24,75</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 32,94</t>
+          <t>21,07; 33,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,59; 27,79</t>
+          <t>17,5; 27,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 28,44</t>
+          <t>20,67; 28,56</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 50,89</t>
+          <t>27,62; 51,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 39,35</t>
+          <t>21,61; 39,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,88; 40,88</t>
+          <t>27,0; 41,11</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-13,38</t>
+          <t>-12,49</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-9,89</t>
+          <t>-10,17</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,74</t>
+          <t>-11,35</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,96; -7,59</t>
+          <t>-19,06; -5,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -5,85</t>
+          <t>-14,25; -6,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,49; -8,1</t>
+          <t>-15,03; -7,67</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-15,27%</t>
+          <t>-14,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,49%</t>
+          <t>-10,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-12,89%</t>
+          <t>-12,46%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,33; -8,72</t>
+          <t>-21,65; -6,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -6,26</t>
+          <t>-14,99; -6,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,03; -8,97</t>
+          <t>-16,46; -8,58</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 8,82</t>
+          <t>-0,55; 8,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,49</t>
+          <t>1,72; 8,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,7</t>
+          <t>2,04; 7,57</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 10,02</t>
+          <t>-0,61; 10,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,42</t>
+          <t>1,82; 9,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,62</t>
+          <t>2,17; 8,5</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-6,43</t>
+          <t>-8,62</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-13,0</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,46</t>
+          <t>-4,22</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -0,87</t>
+          <t>-16,59; -2,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 1,7</t>
+          <t>-4,38; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,22; -1,1</t>
+          <t>-8,36; -0,88</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-6,96%</t>
+          <t>-9,32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-14,18%</t>
+          <t>-0,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,36%</t>
+          <t>-4,58%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -1,09</t>
+          <t>-17,73; -3,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 1,86</t>
+          <t>-4,66; 4,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,92; -1,19</t>
+          <t>-9,0; -1,01</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-1,99</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 11,73</t>
+          <t>-7,28; 9,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 5,39</t>
+          <t>-8,25; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 7,18</t>
+          <t>-5,8; 4,81</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-0,38%</t>
+          <t>-2,24%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>-0,65%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 16,07</t>
+          <t>-8,77; 12,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,3</t>
+          <t>-9,21; 4,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,06</t>
+          <t>-6,68; 5,99</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14,83</t>
+          <t>12,91</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,28</t>
+          <t>11,22</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,81; 20,14</t>
+          <t>7,27; 18,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,18</t>
+          <t>5,77; 14,88</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,76</t>
+          <t>7,78; 15,3</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10,88; 26,56</t>
+          <t>8,76; 24,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,89</t>
+          <t>6,48; 17,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10,25; 19,38</t>
+          <t>9,12; 18,89</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>17,25</t>
+          <t>18,48</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>19,68</t>
+          <t>17,42</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19,23</t>
+          <t>17,96</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,93; 23,21</t>
+          <t>13,1; 23,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14,9; 25,01</t>
+          <t>13,64; 21,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,25; 24,35</t>
+          <t>14,3; 21,22</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,41; 37,72</t>
+          <t>19,43; 37,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>19,56; 35,08</t>
+          <t>17,93; 30,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,45; 36,24</t>
+          <t>20,27; 32,12</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-43,86</t>
+          <t>-29,36</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-24,72</t>
+          <t>-25,35</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-35,94</t>
+          <t>-27,35</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-69,04; -25,89</t>
+          <t>-34,12; -25,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -21,02</t>
+          <t>-28,84; -21,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-56,99; -25,28</t>
+          <t>-30,08; -24,45</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-49,21%</t>
+          <t>-32,94%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-26,19%</t>
+          <t>-26,86%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-39,13%</t>
+          <t>-29,78%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-76,86; -29,23</t>
+          <t>-37,68; -28,29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,93; -22,53</t>
+          <t>-30,45; -23,25</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,12; -27,55</t>
+          <t>-32,62; -26,89</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-6,81</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -0,25</t>
+          <t>-4,14; 0,08</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,35</t>
+          <t>-2,47; 0,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,01</t>
+          <t>-2,84; -0,13</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-8,35%</t>
+          <t>-2,6%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>-1,03%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-4,6%</t>
+          <t>-1,76%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-27,36; -0,3</t>
+          <t>-5,01; 0,12</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 1,54</t>
+          <t>-2,79; 0,76</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -0,03</t>
+          <t>-3,35; -0,16</t>
         </is>
       </c>
     </row>
